--- a/27飞镖项目验收文档-视觉.xlsx
+++ b/27飞镖项目验收文档-视觉.xlsx
@@ -16,9 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="26">
     <font>
       <name val="新細明體"/>
@@ -1254,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>46346</v>
+        <v>46341</v>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
@@ -1304,7 +1302,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>46380</v>
+        <v>46387</v>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
@@ -1354,7 +1352,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>46422</v>
+        <v>46399</v>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
@@ -1404,7 +1402,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>46468</v>
+        <v>46447</v>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>

--- a/27飞镖项目验收文档-视觉.xlsx
+++ b/27飞镖项目验收文档-视觉.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy/m/d"/>
+  </numFmts>
   <fonts count="26">
     <font>
       <name val="新細明體"/>
@@ -682,7 +684,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -706,6 +708,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常規" xfId="0" builtinId="0"/>
@@ -1251,7 +1256,7 @@
       <c r="F4" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="7" t="n">
+      <c r="G4" s="9" t="n">
         <v>46341</v>
       </c>
       <c r="H4" s="6" t="inlineStr">
@@ -1259,7 +1264,7 @@
           <t>跑通镖架瞄准与标定流程</t>
         </is>
       </c>
-      <c r="I4" s="7" t="n">
+      <c r="I4" s="9" t="n">
         <v>46362</v>
       </c>
       <c r="J4" s="6" t="inlineStr">
@@ -1301,7 +1306,7 @@
       <c r="F5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="7" t="n">
+      <c r="G5" s="9" t="n">
         <v>46387</v>
       </c>
       <c r="H5" s="6" t="inlineStr">
@@ -1309,7 +1314,7 @@
           <t>完成前哨站瞄准参数标定</t>
         </is>
       </c>
-      <c r="I5" s="7" t="n">
+      <c r="I5" s="9" t="n">
         <v>46399</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
@@ -1351,7 +1356,7 @@
       <c r="F6" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="7" t="n">
+      <c r="G6" s="9" t="n">
         <v>46399</v>
       </c>
       <c r="H6" s="6" t="inlineStr">
@@ -1359,7 +1364,7 @@
           <t>完成制导镖视觉跟踪与指令下发</t>
         </is>
       </c>
-      <c r="I6" s="7" t="n">
+      <c r="I6" s="9" t="n">
         <v>46446</v>
       </c>
       <c r="J6" s="6" t="inlineStr">
@@ -1401,7 +1406,7 @@
       <c r="F7" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="7" t="n">
+      <c r="G7" s="9" t="n">
         <v>46447</v>
       </c>
       <c r="H7" s="6" t="inlineStr">
@@ -1409,7 +1414,7 @@
           <t>参数化标定与鲁棒性测试</t>
         </is>
       </c>
-      <c r="I7" s="7" t="n">
+      <c r="I7" s="9" t="n">
         <v>46490</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
